--- a/dataset/out/01-vendor-zenith/Zenith_Quotation_ZIS-NBR-2026-1184.xlsx
+++ b/dataset/out/01-vendor-zenith/Zenith_Quotation_ZIS-NBR-2026-1184.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Northbridge Retail</t>
+          <t>Kaveri Retail</t>
         </is>
       </c>
     </row>
